--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.5</v>
+        <v>0.9054054054054054</v>
       </c>
       <c r="B2">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.6546762589928058</v>
       </c>
       <c r="D2">
-        <v>0.5555555555555556</v>
+        <v>0.4173913043478261</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9054054054054054</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6546762589928058</v>
+        <v>0.5746268656716418</v>
       </c>
       <c r="D2">
-        <v>0.4173913043478261</v>
+        <v>0.5089285714285714</v>
       </c>
       <c r="E2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
